--- a/SGC-CKN/Excel/a558581a-0e29-48e8-81be-9bbbe009fc95_Lô_CT-02_P7-103_D800_10-03-2026.xlsx
+++ b/SGC-CKN/Excel/a558581a-0e29-48e8-81be-9bbbe009fc95_Lô_CT-02_P7-103_D800_10-03-2026.xlsx
@@ -143,7 +143,7 @@
 09/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">20:20
+    <t xml:space="preserve">20:10
 09/03/2026</t>
   </si>
   <si>
@@ -153,7 +153,7 @@
     <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
-    <t xml:space="preserve">20:21
+    <t xml:space="preserve">20:11
 09/03/2026</t>
   </si>
   <si>
@@ -1342,13 +1342,13 @@
         <v>-22.7</v>
       </c>
       <c r="H14" s="16">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="I14" s="16">
         <v>4.1</v>
       </c>
       <c r="J14" s="15">
-        <v>3.28</v>
+        <v>3.78</v>
       </c>
       <c r="K14" s="17" t="s">
         <v>30</v>
@@ -1377,13 +1377,13 @@
         <v>-26.6</v>
       </c>
       <c r="H15" s="19">
-        <v>0.65</v>
+        <v>0.82</v>
       </c>
       <c r="I15" s="19">
         <v>3.9</v>
       </c>
-      <c r="J15" s="8">
-        <v>6</v>
+      <c r="J15" s="15">
+        <v>4.78</v>
       </c>
       <c r="K15" s="20" t="s">
         <v>30</v>
@@ -1444,16 +1444,16 @@
         <v>-36.5</v>
       </c>
       <c r="G17" s="25">
-        <v>-39.2</v>
+        <v>-39.21</v>
       </c>
       <c r="H17" s="25">
         <v>0.32</v>
       </c>
       <c r="I17" s="25">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="J17" s="8">
-        <v>8.53</v>
+        <v>8.56</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>30</v>
@@ -1476,7 +1476,7 @@
         <v>56</v>
       </c>
       <c r="F18" s="28">
-        <v>-39.2</v>
+        <v>-39.21</v>
       </c>
       <c r="G18" s="28">
         <v>-40.7</v>
@@ -1485,10 +1485,10 @@
         <v>0.17</v>
       </c>
       <c r="I18" s="28">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="J18" s="8">
-        <v>9</v>
+        <v>8.94</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>57</v>
@@ -1806,13 +1806,13 @@
         <v>-22.7</v>
       </c>
       <c r="G5" s="16">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="H5" s="16">
         <v>4.1</v>
       </c>
       <c r="I5" s="15">
-        <v>3.28</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1835,13 +1835,13 @@
         <v>-26.6</v>
       </c>
       <c r="G6" s="19">
-        <v>0.65</v>
+        <v>0.82</v>
       </c>
       <c r="H6" s="19">
         <v>3.9</v>
       </c>
-      <c r="I6" s="8">
-        <v>6</v>
+      <c r="I6" s="15">
+        <v>4.78</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1890,16 +1890,16 @@
         <v>-36.5</v>
       </c>
       <c r="F8" s="25">
-        <v>-39.2</v>
+        <v>-39.21</v>
       </c>
       <c r="G8" s="25">
         <v>0.32</v>
       </c>
       <c r="H8" s="25">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="I8" s="8">
-        <v>8.53</v>
+        <v>8.56</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1916,7 +1916,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-39.2</v>
+        <v>-39.21</v>
       </c>
       <c r="F9" s="28">
         <v>-40.7</v>
@@ -1925,10 +1925,10 @@
         <v>0.17</v>
       </c>
       <c r="H9" s="28">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="I9" s="8">
-        <v>9</v>
+        <v>8.94</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
